--- a/data/availability/projects/emaar-misr/belle-vie.xlsx
+++ b/data/availability/projects/emaar-misr/belle-vie.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for belle-vie</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1537,7 +1547,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1587,7 +1597,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1637,7 +1647,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1687,7 +1697,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1737,7 +1747,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1787,7 +1797,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1909,7 +1919,6 @@
       <c r="G2" t="n">
         <v>120</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1920,7 +1929,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1966,7 +1975,6 @@
       <c r="G3" t="n">
         <v>120</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1977,7 +1985,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2023,7 +2031,6 @@
       <c r="G4" t="n">
         <v>120</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2034,7 +2041,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2080,7 +2087,6 @@
       <c r="G5" t="n">
         <v>361</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2137,7 +2143,6 @@
       <c r="G6" t="n">
         <v>310.2</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2194,7 +2199,6 @@
       <c r="G7" t="n">
         <v>447</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2251,7 +2255,6 @@
       <c r="G8" t="n">
         <v>344.5</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2308,7 +2311,6 @@
       <c r="G9" t="n">
         <v>310.2</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2365,7 +2367,6 @@
       <c r="G10" t="n">
         <v>347.4</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2422,7 +2423,6 @@
       <c r="G11" t="n">
         <v>310.9</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2479,7 +2479,6 @@
       <c r="G12" t="n">
         <v>377.1</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2536,7 +2535,6 @@
       <c r="G13" t="n">
         <v>329.2</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2593,7 +2591,6 @@
       <c r="G14" t="n">
         <v>427.2</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2650,7 +2647,6 @@
       <c r="G15" t="n">
         <v>746.2</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2707,7 +2703,6 @@
       <c r="G16" t="n">
         <v>370.8</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2764,7 +2759,6 @@
       <c r="G17" t="n">
         <v>311.7</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2821,7 +2815,6 @@
       <c r="G18" t="n">
         <v>307</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2878,7 +2871,6 @@
       <c r="G19" t="n">
         <v>341.2</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2935,7 +2927,6 @@
       <c r="G20" t="n">
         <v>319.8</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2992,7 +2983,6 @@
       <c r="G21" t="n">
         <v>319.6</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3049,7 +3039,6 @@
       <c r="G22" t="n">
         <v>384.2</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3106,7 +3095,6 @@
       <c r="G23" t="n">
         <v>384.2</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3163,7 +3151,6 @@
       <c r="G24" t="n">
         <v>384.2</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3220,7 +3207,6 @@
       <c r="G25" t="n">
         <v>384.2</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3277,7 +3263,6 @@
       <c r="G26" t="n">
         <v>337</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3334,7 +3319,6 @@
       <c r="G27" t="n">
         <v>336.6</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3391,7 +3375,6 @@
       <c r="G28" t="n">
         <v>324.2</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3448,7 +3431,6 @@
       <c r="G29" t="n">
         <v>343.5</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3505,7 +3487,6 @@
       <c r="G30" t="n">
         <v>389.3</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3562,7 +3543,6 @@
       <c r="G31" t="n">
         <v>387.8</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3619,7 +3599,6 @@
       <c r="G32" t="n">
         <v>386.9</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3676,7 +3655,6 @@
       <c r="G33" t="n">
         <v>405.1</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3733,7 +3711,6 @@
       <c r="G34" t="n">
         <v>331.4</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3790,7 +3767,6 @@
       <c r="G35" t="n">
         <v>334.7</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3847,7 +3823,6 @@
       <c r="G36" t="n">
         <v>343</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3904,7 +3879,6 @@
       <c r="G37" t="n">
         <v>383.4</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3961,7 +3935,6 @@
       <c r="G38" t="n">
         <v>383.4</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4018,7 +3991,6 @@
       <c r="G39" t="n">
         <v>376.1</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4075,7 +4047,6 @@
       <c r="G40" t="n">
         <v>378.3</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4132,7 +4103,6 @@
       <c r="G41" t="n">
         <v>375</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4189,7 +4159,6 @@
       <c r="G42" t="n">
         <v>376.1</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4246,7 +4215,6 @@
       <c r="G43" t="n">
         <v>456.6</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4303,7 +4271,6 @@
       <c r="G44" t="n">
         <v>293</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4314,7 +4281,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4360,7 +4327,6 @@
       <c r="G45" t="n">
         <v>271</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4371,7 +4337,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4417,7 +4383,6 @@
       <c r="G46" t="n">
         <v>196</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4428,7 +4393,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4474,7 +4439,6 @@
       <c r="G47" t="n">
         <v>193</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4485,7 +4449,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4531,7 +4495,6 @@
       <c r="G48" t="n">
         <v>196</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4542,7 +4505,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4588,7 +4551,6 @@
       <c r="G49" t="n">
         <v>193</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4599,7 +4561,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4645,7 +4607,6 @@
       <c r="G50" t="n">
         <v>283</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4656,7 +4617,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4702,7 +4663,6 @@
       <c r="G51" t="n">
         <v>193</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4713,7 +4673,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4759,7 +4719,6 @@
       <c r="G52" t="n">
         <v>273</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4770,7 +4729,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4816,7 +4775,6 @@
       <c r="G53" t="n">
         <v>411</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4827,7 +4785,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4873,7 +4831,6 @@
       <c r="G54" t="n">
         <v>454</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4884,7 +4841,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4930,7 +4887,6 @@
       <c r="G55" t="n">
         <v>120</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4941,7 +4897,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4987,7 +4943,6 @@
       <c r="G56" t="n">
         <v>120</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4998,7 +4953,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5044,7 +4999,6 @@
       <c r="G57" t="n">
         <v>120</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5055,7 +5009,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5101,7 +5055,6 @@
       <c r="G58" t="n">
         <v>120</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5112,7 +5065,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5158,7 +5111,6 @@
       <c r="G59" t="n">
         <v>120</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5169,7 +5121,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5215,7 +5167,6 @@
       <c r="G60" t="n">
         <v>120</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5226,7 +5177,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5272,7 +5223,6 @@
       <c r="G61" t="n">
         <v>120</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5283,7 +5233,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5329,7 +5279,6 @@
       <c r="G62" t="n">
         <v>120</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5340,7 +5289,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5386,7 +5335,6 @@
       <c r="G63" t="n">
         <v>120</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5397,7 +5345,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5443,7 +5391,6 @@
       <c r="G64" t="n">
         <v>120</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5454,7 +5401,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5500,7 +5447,6 @@
       <c r="G65" t="n">
         <v>120</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5511,7 +5457,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5557,7 +5503,6 @@
       <c r="G66" t="n">
         <v>120</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5568,7 +5513,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5614,7 +5559,6 @@
       <c r="G67" t="n">
         <v>120</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5625,7 +5569,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5671,7 +5615,6 @@
       <c r="G68" t="n">
         <v>120</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5682,7 +5625,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5728,7 +5671,6 @@
       <c r="G69" t="n">
         <v>120</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5739,7 +5681,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5785,7 +5727,6 @@
       <c r="G70" t="n">
         <v>120</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5796,7 +5737,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5842,7 +5783,6 @@
       <c r="G71" t="n">
         <v>120</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5853,7 +5793,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5899,7 +5839,6 @@
       <c r="G72" t="n">
         <v>120</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5910,7 +5849,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5956,7 +5895,6 @@
       <c r="G73" t="n">
         <v>120</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5967,7 +5905,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6013,7 +5951,6 @@
       <c r="G74" t="n">
         <v>120</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6024,7 +5961,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6070,7 +6007,6 @@
       <c r="G75" t="n">
         <v>120</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6081,7 +6017,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6127,7 +6063,6 @@
       <c r="G76" t="n">
         <v>120</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6138,7 +6073,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6184,7 +6119,6 @@
       <c r="G77" t="n">
         <v>120</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6195,7 +6129,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6241,7 +6175,6 @@
       <c r="G78" t="n">
         <v>120</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6252,7 +6185,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6298,7 +6231,6 @@
       <c r="G79" t="n">
         <v>120</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6309,7 +6241,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6355,7 +6287,6 @@
       <c r="G80" t="n">
         <v>120</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6366,7 +6297,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6412,7 +6343,6 @@
       <c r="G81" t="n">
         <v>120</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6423,7 +6353,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6469,7 +6399,6 @@
       <c r="G82" t="n">
         <v>120</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6480,7 +6409,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6526,7 +6455,6 @@
       <c r="G83" t="n">
         <v>120</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6537,7 +6465,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6583,7 +6511,6 @@
       <c r="G84" t="n">
         <v>120</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6594,7 +6521,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6640,7 +6567,6 @@
       <c r="G85" t="n">
         <v>120</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6651,7 +6577,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6697,7 +6623,6 @@
       <c r="G86" t="n">
         <v>120</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6708,7 +6633,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6754,7 +6679,6 @@
       <c r="G87" t="n">
         <v>120</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6765,7 +6689,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6811,7 +6735,6 @@
       <c r="G88" t="n">
         <v>120</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6822,7 +6745,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6868,7 +6791,6 @@
       <c r="G89" t="n">
         <v>120</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6879,7 +6801,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6925,7 +6847,6 @@
       <c r="G90" t="n">
         <v>120</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6936,7 +6857,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6982,7 +6903,6 @@
       <c r="G91" t="n">
         <v>120</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6993,7 +6913,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7039,7 +6959,6 @@
       <c r="G92" t="n">
         <v>120</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7050,7 +6969,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7096,7 +7015,6 @@
       <c r="G93" t="n">
         <v>120</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7107,7 +7025,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7153,7 +7071,6 @@
       <c r="G94" t="n">
         <v>120</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7164,7 +7081,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7210,7 +7127,6 @@
       <c r="G95" t="n">
         <v>120</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7221,7 +7137,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7267,7 +7183,6 @@
       <c r="G96" t="n">
         <v>120</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7278,7 +7193,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7324,7 +7239,6 @@
       <c r="G97" t="n">
         <v>120</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7335,7 +7249,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7381,7 +7295,6 @@
       <c r="G98" t="n">
         <v>857</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7392,7 +7305,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">

--- a/data/availability/projects/emaar-misr/belle-vie.xlsx
+++ b/data/availability/projects/emaar-misr/belle-vie.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
